--- a/data/Comparing_Dynamics.xlsx
+++ b/data/Comparing_Dynamics.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="ICML_runs" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Unireps" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="218">
   <si>
     <t>Datset</t>
   </si>
@@ -530,13 +531,148 @@
   </si>
   <si>
     <t>eager-river-301</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>batch_size</t>
+  </si>
+  <si>
+    <t>lr</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>efficient-sun-423</t>
+  </si>
+  <si>
+    <t>treasured-snowflake-422</t>
+  </si>
+  <si>
+    <t>dazzling-mountain-421</t>
+  </si>
+  <si>
+    <t>visionary-terrain-420</t>
+  </si>
+  <si>
+    <t>azure-blaze-419</t>
+  </si>
+  <si>
+    <t>pretty-lake-418</t>
+  </si>
+  <si>
+    <t>polar-elevator-417</t>
+  </si>
+  <si>
+    <t>mild-butterfly-416</t>
+  </si>
+  <si>
+    <t>usual-violet-415</t>
+  </si>
+  <si>
+    <t>worldly-wind-414</t>
+  </si>
+  <si>
+    <t>icy-lake-413</t>
+  </si>
+  <si>
+    <t>vocal-totem-412</t>
+  </si>
+  <si>
+    <t>logical-eon-411</t>
+  </si>
+  <si>
+    <t>avid-fog-409</t>
+  </si>
+  <si>
+    <t>revived-brook-408</t>
+  </si>
+  <si>
+    <t>spring-meadow-407</t>
+  </si>
+  <si>
+    <t>laced-galaxy-406</t>
+  </si>
+  <si>
+    <t>clear-snowball-405</t>
+  </si>
+  <si>
+    <t>bright-oath-404</t>
+  </si>
+  <si>
+    <t>honest-aardvark-401</t>
+  </si>
+  <si>
+    <t>snowy-lake-400</t>
+  </si>
+  <si>
+    <t>fluent-armadillo-399</t>
+  </si>
+  <si>
+    <t>super-armadillo-398</t>
+  </si>
+  <si>
+    <t>rich-jazz-397</t>
+  </si>
+  <si>
+    <t>young-armadillo-396</t>
+  </si>
+  <si>
+    <t>proud-resonance-395</t>
+  </si>
+  <si>
+    <t>kind-jazz-394</t>
+  </si>
+  <si>
+    <t>sleek-bird-393</t>
+  </si>
+  <si>
+    <t>silver-lion-392</t>
+  </si>
+  <si>
+    <t>smooth-hill-391</t>
+  </si>
+  <si>
+    <t>kind-armadillo-390</t>
+  </si>
+  <si>
+    <t>cerulean-bird-389</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -601,6 +737,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -715,7 +856,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="54">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -842,6 +983,42 @@
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -901,18 +1078,26 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
+  <tableStyles count="2">
     <tableStyle count="4" pivot="0" name="ICML_runs-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
+    <tableStyle count="2" pivot="0" name="Unireps-style">
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
   </tableStyles>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -931,6 +1116,19 @@
     <tableColumn name="Learning Rate" id="6"/>
   </tableColumns>
   <tableStyleInfo name="ICML_runs-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:E91" displayName="Table_1" name="Table_1" id="2">
+  <tableColumns count="5">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
+  </tableColumns>
+  <tableStyleInfo name="Unireps-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -10120,4 +10318,1566 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="45">
+        <v>128.0</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="45">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="47">
+        <v>128.0</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="47">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="45">
+        <v>128.0</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="45">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="47">
+        <v>128.0</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="47">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="45">
+        <v>128.0</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="45">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="47">
+        <v>128.0</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="47">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="45">
+        <v>128.0</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="45">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="47">
+        <v>128.0</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="47">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="45">
+        <v>128.0</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="45">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="47">
+        <v>128.0</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="47">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="49">
+        <v>32.0</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="51">
+        <v>32.0</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="49">
+        <v>32.0</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="49">
+        <v>32.0</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="49">
+        <v>32.0</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="49">
+        <v>32.0</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="49">
+        <v>64.0</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="49">
+        <v>64.0</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="49">
+        <v>64.0</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="51">
+        <v>64.0</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="49">
+        <v>64.0</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="49">
+        <v>64.0</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C37" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C38" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="51">
+        <v>1024.0</v>
+      </c>
+      <c r="C41" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="49">
+        <v>1024.0</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="51">
+        <v>1024.0</v>
+      </c>
+      <c r="C43" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="49">
+        <v>1024.0</v>
+      </c>
+      <c r="C44" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="51">
+        <v>1024.0</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="49">
+        <v>1024.0</v>
+      </c>
+      <c r="C46" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C47" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C48" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C49" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C50" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="49">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="51">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C52" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C53" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C54" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="49">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C55" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="51">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="B56" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C56" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="49">
+        <v>128.0</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="49">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" s="51">
+        <v>128.0</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="51">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B60" s="52">
+        <v>1024.0</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C61" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B62" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C62" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C63" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="B66" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C66" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" s="53">
+        <v>64.0</v>
+      </c>
+      <c r="C67" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="B68" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C68" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D68" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C70" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C71" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D71" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B72" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C72" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D72" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B73" s="53">
+        <v>1024.0</v>
+      </c>
+      <c r="C73" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C74" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E74" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="53">
+        <v>32.0</v>
+      </c>
+      <c r="C75" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48" t="s">
+        <v>202</v>
+      </c>
+      <c r="B76" s="52">
+        <v>64.0</v>
+      </c>
+      <c r="C76" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="B77" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C77" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" s="53">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="B78" s="52">
+        <v>32.0</v>
+      </c>
+      <c r="C78" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" s="53">
+        <v>1024.0</v>
+      </c>
+      <c r="C79" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C80" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E80" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="B81" s="53">
+        <v>64.0</v>
+      </c>
+      <c r="C81" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E81" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="B82" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C82" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D82" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" s="52">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="B83" s="53">
+        <v>32.0</v>
+      </c>
+      <c r="C83" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E83" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="B84" s="52">
+        <v>1024.0</v>
+      </c>
+      <c r="C84" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C85" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C86" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="B87" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C87" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D87" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" s="52">
+        <v>64.0</v>
+      </c>
+      <c r="C88" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" s="53">
+        <v>128.0</v>
+      </c>
+      <c r="C89" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E89" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" s="52">
+        <v>128.0</v>
+      </c>
+      <c r="C90" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" s="52">
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="B91" s="53">
+        <v>32.0</v>
+      </c>
+      <c r="C91" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" s="53">
+        <v>39.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>